--- a/erp-server/erp-server-scm/src/main/resources/excel/supplierVisit.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/supplierVisit.xlsx
@@ -27,9 +27,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -45,6 +52,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -70,7 +84,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>拜访时间</t>
+      <t>拜访时间(yyyy-MM-dd格式)(多个请用英文逗号隔开)</t>
     </r>
   </si>
   <si>
@@ -85,14 +99,21 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>拜访人</t>
+      <t>拜访人(多个请用英文逗号隔开)</t>
     </r>
   </si>
   <si>
-    <t>拜访物料</t>
+    <t>拜访物料(多个请用英文逗号隔开)</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -108,6 +129,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -120,6 +148,18 @@
       </rPr>
       <t>拜访结果</t>
     </r>
+  </si>
+  <si>
+    <t>七七供应商</t>
+  </si>
+  <si>
+    <t>新品</t>
+  </si>
+  <si>
+    <t>陈锦辉</t>
+  </si>
+  <si>
+    <t>待定</t>
   </si>
 </sst>
 </file>
@@ -756,7 +796,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -764,6 +804,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1085,8 +1128,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="20.875" customWidth="1"/>
     <col min="2" max="7" width="17.375" customWidth="1"/>
@@ -1115,12 +1158,36 @@
         <v>6</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3">
+        <v>45818</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2">
+        <v>2028</v>
+      </c>
+      <c r="F2">
+        <v>123</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1">
-      <formula1>"新品,准入,其它"</formula1>
+  <dataValidations count="3">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1 G1"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
+      <formula1>"新品,准入,其他"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
       <formula1>"合格,不合格,待定"</formula1>
     </dataValidation>
   </dataValidations>

--- a/erp-server/erp-server-scm/src/main/resources/excel/supplierVisit.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/supplierVisit.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <r>
       <rPr>
@@ -74,6 +74,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -89,6 +96,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -150,13 +164,19 @@
     </r>
   </si>
   <si>
-    <t>七七供应商</t>
+    <t>供应商</t>
   </si>
   <si>
     <t>新品</t>
   </si>
   <si>
-    <t>陈锦辉</t>
+    <t>2025-10-11</t>
+  </si>
+  <si>
+    <t>张三,李四</t>
+  </si>
+  <si>
+    <t>2028,2029</t>
   </si>
   <si>
     <t>待定</t>
@@ -800,13 +820,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1131,61 +1151,62 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="20.875" customWidth="1"/>
-    <col min="2" max="7" width="17.375" customWidth="1"/>
+    <col min="1" max="1" width="20.875" style="1" customWidth="1"/>
+    <col min="2" max="7" width="17.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3">
-        <v>45818</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2">
-        <v>2028</v>
-      </c>
-      <c r="F2">
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1">
         <v>123</v>
       </c>
-      <c r="G2" t="s">
-        <v>10</v>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1 G1"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1048576">
-      <formula1>"新品,准入,其他"</formula1>
+      <formula1>"新品,准入,其它"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G1048576">
       <formula1>"合格,不合格,待定"</formula1>
